--- a/disease_registry/outputs/Wheat/internet.xlsx
+++ b/disease_registry/outputs/Wheat/internet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disease Registry" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Disease Registry" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,27 +456,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dwarf_Bunt</t>
+          <t>Barley_Yellow_Dwarf_Virus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tilletia controversa</t>
+          <t>Barley yellow dwarf virus (BYDV) — multiple species in family Luteoviridae</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fungal</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Foliar, Seed, Stem, Whole plant</t>
+          <t>Foliar, Whole plant</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Early spring symptoms include abnormally high tillers and yellow spots or streaks in leaves. At soft dough stage and beyond, the disease is identified by 50% plant height reduction (dwarfing), black dough pushed from seed heads, fishlike smell, and kernels replaced with bunt balls causing glumes to splay and appear ragged.. 50% reduction in plant height; black dough that can be pushed from seed heads; fishlike smell present in dough; kernels replaced with bunt balls causing glumes to splay and look ragged; presence of spherical bunt balls distinguishes the disease from abiotic disorders such as nutrient deficiencies, chemical injury, and soil compaction.. Common bunt</t>
+          <t>Yellowing, reddening, or purpling of leaf tips progressing to full leaves, with plant dwarfing in early infections. Leaves may become stiff and erect with inward-rolling necrotic margins. Affected plants appear singly or in small patches among normal plants.. Reddish-purple or yellowish discoloration of the flag leaf; yellowing patches visible in fields often in circular patterns; color varies by host: red to purple in oats, yellow to red in wheat, bright yellow in barley. Does not produce a distinct mosaic pattern. Pale yellowing of older leaf tips is typical; during cool temperatures the tips can become reddish-purple.. Wheat streak mosaic, Soil-borne mosaic, Mineral/nutrient deficiencies, Low temperature damage, Root and crown diseases, Herbicide injury, Environmental stress</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -485,18 +485,18 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Common_Bunt</t>
+          <t>Cephalosporium_Stripe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tilletia caries and Tilletia laevis</t>
+          <t>Cephalosporium gramineum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,8 +504,16 @@
           <t>Fungal</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Root, Vascular, Seed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yellow stripes running from the tip of the leaf blade to its base and down the leaf sheath, with brown necrotic streaks developing in the center of the stripes as leaves age. Infected stems are stunted causing a double-canopy of healthy and infected heads. Severely infected stems die prematurely resulting in dull-colored whiteheads containing only shriveled grain.. Distinct yellow stripes (one to three per leaf) extending the full length of the leaf blade and down the leaf sheath, with brown necrotic streaks in the center representing colonized xylem tissue. Vascular bundles are brown within the yellow stripes along affected leaf sheaths and joints are darkened inside. Whiteheads are dull-colored rather than bright straw-colored. No powdery spores present in the stripes.. Stripe rust</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>high</t>
@@ -518,12 +526,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Eyespot</t>
+          <t>Common_Bunt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oculimacula yallundae and Oculimacula acuformis</t>
+          <t>Tilletia tritici and T. laevis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,12 +541,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stem, Foliar</t>
+          <t>Seed, Whole plant, Foliar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Eyespot produces characteristic elliptical or eye-shaped lesions on the lower stem with a dark brown perimeter and yellowish-brown center, often leading to stem weakening and lodging in severe infections. Stems can also die standing, resulting in whiteheads.. Elliptical or eye-shaped lesions with a distinct dark brown perimeter, yellowish-brown center with dark brown-blackish fruiting bodies, and whitish-gray mycelium visible in severe infections when the stem is bisected. Multi-directional lodging pattern distinct from wind damage. Broken stems showing dark brown charred appearance with scurf present.. Sharp eyespot of wheat</t>
+          <t>Spikelets develop off-green discoloration and appear greasy as heads ripen. Glumes open as if overstuffed as large spore masses (bunt balls) form within spikelets, eventually rupturing the seed coat to reveal large masses of black spores. Light brown smut balls filled with dark brown spore masses replace kernels in infected heads, releasing a distinctive foul fishy odor when crushed. Plants may be slightly stunted with distorted glumes and heads that remain green longer.. Bunt balls roughly the shape of a wheat kernel (not globular) with black spores and a distinct fishy odor; no positive symptoms apparent until the crop heads; infected heads thinner and remain green longer; awns of infected heads may be smaller or completely missing; plants not severely stunted.. Dwarf Bunt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -553,35 +561,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sharp_Eyespot</t>
+          <t>Dwarf_Bunt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rhizoctonia cerealis</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>Tilletia controversa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Foliar, Seed, Whole plant</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Infected plants are stunted with excessive tillering and yellow leaf flecking at late seedling stage. Once heads emerge, kernels are transformed into spherical bunt balls filled with dark colored spores having a fishy odor. Infected heads maintain green color longer, with noticeably splayed spikes and awns.. Spherical bunt balls (distinguishing from common bunt's kernel-shaped balls) in heads with a characteristic fishy odor; plant stunting notably dwarfed compared to healthy plants; smut balls emit a distinctive foul odor when crushed.. Common Bunt (Stinking Smut), nutrient deficiencies, chemical injury, soil compaction, Loose Smut of Wheat</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cephalosporium_Stripe</t>
+          <t>Eyespot</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cephalosporium gramineum</t>
+          <t>Oculimacula yallundae / Oculimacula acuformis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -591,12 +611,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Vascular</t>
+          <t>Stem, Vascular</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yellowish stripes appear on leaves and leaf sheaths at any growth stage, with seedlings showing mosaic-like yellowing in early spring. Typically two to three long yellow stripes per leaf run from the tip of the blade down to the sheath, each connected to a darkened vein. Brown necrotic streaks develop in stripe centers as leaves age. Infected stems are stunted, creating a double-canopy effect, and severely infected stems die prematurely, resulting in whiteheads with empty or shriveled kernels.. A diagnostic feature is that vascular bundles are brown within the yellow stripes along affected leaf sheaths, and the joints are darkened inside. Necrotic areas appear on stems. Yellow stripes extend the full length of the leaf blade and down the leaf sheath, distinguishable from stripe rust by the absence of powdery yellow-orange spores.. Stripe rust, Leaf spot diseases, Wheat streak mosaic</t>
+          <t>Characteristic elliptical or eye-shaped lesions on the lower stem with a dark brown perimeter and yellowish-brown center; severe infections show whitish-gray mycelium inside the hollow stem and may cause multidirectional lodging and premature white heads.. Elliptical (eye-shaped) lesions on the lower stem with a dark brown perimeter separating healthy and infected tissue; yellowish-brown lesion center with dark brown-blackish pseudoparenchyma fruiting bodies; whitish-gray mycelium visible inside the hollow stem in severe infections; brittle lesion tissue causing multidirectional lodging; lodged stems break off at soil line when pulled.. Sharp eyespot (Rhizoctonia cerealis)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -605,23 +625,35 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Barley_Yellow_Dwarf_Virus</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>Foot_Rot</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fusarium spp.</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Root, Stem, Seed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Brown discoloration of roots and subcrown internode progressing to dark brown at boot stage; dark brown to red lesion near the first node; pink cottony fungal growth inside lower stems; premature white heads with shriveled or absent kernels.. Dark brown to red lesion near the first node; pink, cottony fungal growth inside lower stems; infected crowns spongy and heavily decayed under humid conditions; infected seedlings reddish with poor vigor and poor tiller production; lower stem above first node streaked or uniformly brown.. Common Root Rot (Seedling Blight), Eyespot (Strawbreaker Foot Rot)</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>high</t>
@@ -634,20 +666,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wheat_Bunt</t>
+          <t>Sharp_Eyespot</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tilletia tritici</t>
+          <t>Rhizoctonia cerealis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Seed</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
@@ -661,16 +689,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wheat_Stripe_Rust</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>Glume_Blotch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Parastagonospora nodorum</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Foliar, Stem</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Small yellow spots that enlarge into oval or 'cat eye' shaped lesions with dark-brown centers on leaves; infected glumes appear dirty from a distance and are purple to brown in color.. Oval or 'cat eye' shaped lesions with dark-brown centers on leaves; glumes that appear dirty and are purple to brown in color.</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -680,105 +724,137 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Head_Scab</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>Alternaria_Blight</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alternaria triticina</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Foliar, Leaf sheath, Awns, Glumes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Small, oval, chlorotic lesions irregularly scattered on leaves that enlarge into dark brown or grey sunken lesions, eventually merging and killing the entire leaf. In severe cases, leaf sheaths, awns and glumes have a burnt appearance.. Lesions are oval and chlorotic initially, becoming irregular, dark brown or grey and sunken, with a bright yellow marginal zone, up to 1 cm or more in diameter. Under moist conditions, lesions may be covered by black powdery conidia. In severe cases, leaf sheaths, awns and glumes have a burnt appearance.</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Loose_Smut</t>
+          <t>Bacterial_Leaf_Streak_Black_Chaff</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ustilago tritici</t>
+          <t>Xanthomonas translucens</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fungal</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Glumes, Rachis, Peduncle, Seed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Small water-soaked lesions on leaves that develop into long, thin, tan-brown streaks confined between veins, with milky bacterial ooze that dries to a scale-like glaze; on heads, dark brown to black discoloration of the peduncle, rachis, and glumes (black chaff).. Lesions are translucent when backlit; milky droplets of bacterial ooze within lesions when free moisture is present; dried ooze gives a shiny or glazed appearance with small amber-colored granules; lesions confined between leaf veins; symptoms most evident on the middle third of the leaf blade; alternating bands of green and pigmented awn tissue in awned varieties; streaked lesions (not spotty or blotchy).. Bacterial leaf blight (Pseudomonas syringae), Pseudo black chaff (melanosis)</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Glume_Blotch</t>
+          <t>Bacterial_Streak</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Parastagonospora nodorum</t>
+          <t>Pseudomonas syringae</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fungal</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Foliar, Stem</t>
+          <t>Foliar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Small yellow spots in the lower canopy enlarge into oval or cat eye shaped lesions with dark-brown centers on leaves. Infected glumes develop gray-brown blotches starting at the tips, with aged blotches showing dark pin-point pycnidia. Infected heads develop low test weight due to shriveled grain.. Dark pin-point structures called pycnidia visible under 10X magnification on discolored glumes are the best diagnostic sign; leaves show distinctive oval or cat eye shaped lesions with dark-brown centers.</t>
+          <t>Spotty and blotchy leaf lesions, in contrast to the streaked lesions of bacterial leaf streak.. Spotty and blotchy leaf lesions rather than the long, thin, streaked lesions characteristic of bacterial leaf streak.. Bacterial leaf streak (Xanthomonas translucens)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alternaria_Blight</t>
+          <t>Head_Scab</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alternaria triticina</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>Fusarium graminearum</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Seed, Stem</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alternaria Leaf Spot caused by NY Alternaria isolates, black point caused by A. infectoria, foliar blights caused by A. triticimaculans, foliar blights caused by A. hungarica</t>
+          <t>Diseased spikelets turn light-straw colored and bleached while healthy spikelets remain green. Infected kernels are shrunken, wrinkled, light-weight, and discolored, ranging from light-brown to pink to grayish white. Pink or orange spore masses can be observed on infected spikelets, particularly at the base.. Pinkish to salmon-colored spore masses (sporodochia) form on the margin of the glumes near the base of the spikelet, best seen early in the morning before dew dries. Dark purplish-black fruiting bodies (perithecia) may appear on mature heads in cool, moist weather. Shriveled, chalky, white-pink discolored 'tombstone' kernels are lightweight and highly contaminated with mycotoxins.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -788,27 +864,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bacterial_Leaf_Streak_Black_Chaff</t>
+          <t>Karnal_Bunt</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xanthomonas translucens</t>
+          <t>Tilletia indica</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Fungal</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Seed</t>
+          <t>Seed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dark brown, water-soaked streaks appear on leaves with milky bacterial exudate that dries into a scale-like glaze. Black-brown discolorations develop on glumes. Cream to yellow bacterial ooze is produced on infected parts during wet or humid weather, appearing light-colored and scale-like when dry.. Black chaff can be distinguished from other diseases by the appearance of cream to yellow bacterial ooze in the form of slime or viscous droplets produced on infected plant parts during wet or humid weather. This ooze appears light colored and scale-like when dry. Bands of necrotic and healthy tissue on awns ('barber's pole') are indicative of black chaff.. Bacterial leaf blight (Pseudomonas syringae), Pseudo black chaff, Genetic melanism, Glume Blotch</t>
+          <t>Harvested seeds contain tissue that is gray at first but later turns black, with discoloration often limited to the embryo end but sometimes extending over the entire kernel. In advanced infections kernels are blackened, sooty, and fragile, resembling a boat or dugout canoe shape, and may produce a strong fishy smell.. Blackened, sooty kernels with cracked outer layer revealing black powder when pressed; advanced infections produce a boat or dugout canoe shape; severe infections produce trimethylamine giving a strong fishy odor. Requires microscope and biochemical tests for accurate field identification.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -823,12 +899,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wheat_Leaf_Rust</t>
+          <t>Stem_Rust</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Puccinia triticina Eriks.</t>
+          <t>Puccinia graminis f. sp. tritici</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -838,12 +914,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Foliar, Stem</t>
+          <t>Leaf sheaths, Stem, Spike, Leaves</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Small circular to oval yellow-orange colored pustules on leaves giving a rusty appearance, progressing to brown-black teliospores as the plant matures.. Small circular to oval yellow-orange pustules that give a characteristic rusty appearance to leaves.</t>
+          <t>Pustules (uredinia) containing red to orange spores erupt from stem and leaf tissue; uredinia are brick red, oval, and rupture the host epidermis with infected areas rough to the touch. The emerging spores tear tissue giving pustules a characteristic tattered appearance.. Brick red oval uredinia that rupture the epidermis, sporulating on both leaf surfaces, with infected areas rough to the touch. Spores are a deeper red color than leaf rust and stripe rust. Grain is shriveled due to damage to conducting tissue and severe disease can cause straw breakage. Pustules can also be found on glumes and awns.. Leaf Rust, Stripe Rust</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -852,33 +928,33 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Wheat_Streak_Mosaic_Virus</t>
+          <t>Stripe_Rust</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wheat Streak Mosaic Virus (WSMV)</t>
+          <t>Puccinia striiformis f. sp. tritici</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Fungal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Foliar, Whole plant</t>
+          <t>Leaves, Leaf sheaths, Glumes, Awns, Spike</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Leaves of infected plants show a yellowed mosaic pattern of parallel discontinuous streaks that progress to mottled yellow. Infected plants are typically stunted, may be splayed on the ground, and do not tiller as well as unaffected plants. Light green and dark-green or yellow and green mosaics coalesce into streaks characteristic of this disease.. The streaked mosaic pattern on leaves and the rosette appearance of plants are distinctive field diagnostic symptoms. Yellow streaks run parallel to leaf veins; mosaics coalesce into streaks, and in severe reactions streaks may become necrotic. Tightly rolled and trapped leaves may also be evident from wheat curl mite feeding damage. Mite-infested leaves have edges rolled inward toward the mid-rib, and the developing leaf is often curled back on itself, forming a loop.</t>
+          <t>Yellow streaks (pre-pustules) followed by small, bright yellow, elongated uredial pustules arranged in conspicuous rows (stripes) on leaves, leaf sheaths, glumes and awns. Small yellowish uredinia appear in linear rows on the leaf; a single infection can result in a stripe the length of the leaf. Stunting of plants is common with severe early infections.. Bright yellow elongated pustules arranged in conspicuous linear rows (stripes) on leaves, releasing yellow-orange masses of urediniospores when mature. A single infection can produce a stripe the full length of the leaf. In some varieties, long, narrow yellow stripes develop on leaves.. Leaf rust, Stem rust</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -887,18 +963,18 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Powdery_Mildew</t>
+          <t>Loose_Smut</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blumeria graminis f. sp. tritici</t>
+          <t>Ustilago tritici</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -906,26 +982,34 @@
           <t>Fungal</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Foliar, Seed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Affected plants head early, producing sterile heads with clumped, sooty olive-black spores replacing healthy glumes and kernels. Prior to heading, mild symptoms include yellowish leaf streaks and stiff, dark green leaves.. Sterile heads with sooty olive-black spores in place of glumes and kernels; after spore dispersal, only a bare rachis remains with a few fragments of glumes or awns. Loose smut spores will NOT have a fishy odor.</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karnal_Bunt</t>
+          <t>Powdery_Mildew</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tilletia indica</t>
+          <t>Blumeria graminis f. sp. tritici</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -933,8 +1017,16 @@
           <t>Fungal</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Foliar, Stem</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Powdery white to gray fungal growth on upper leaf surfaces and stems, with fluffy white pustules first appearing on lowest leaves, later changing to grey-brown color. Yellow leaf tissue develops on the opposite side of the mold growth. Small black fruiting bodies (cleistothecia) develop in older grey colonies as plants mature.. White to gray cottony patches on upper leaf surfaces producing large quantities of small asexual conidia (oidia) in long chains; yellow leaf tissue on the opposite side of the mold growth turning tan or brown; distinct round black dots (cleistothecia) within older grey colonies of powdery mildew.</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>high</t>
@@ -947,60 +1039,64 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rhizoctonia_Damping-Off</t>
+          <t>Pythium_Diseases</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rhizoctonia solani</t>
+          <t>Pythium spp. / Globisporangium spp.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fungal</t>
+          <t>Oomycete</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Root, Stem, Seed</t>
+          <t>Root, Whole plant</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Highly virulent isolates cause characteristic water soaked lesions on roots and hypocotyl, stunting of plant growth, root necrosis and cortex tissue maceration, and subsequent death. Characteristic water soaked lesions on the root and hypocotyl; root necrosis and cortex tissue maceration</t>
+          <t>Plants show stunting, yellowing, tiller reduction, and poor stand. Infected roots are shorter, have few root hairs, and are necrotic, with the outer root cortex falling off easily.. The outer layer of the root (the cortex) falls off easily on infected plants, and roots are shorter with few root hairs.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Foot_Rot</t>
+          <t>Wheat_Streak_Mosaic_Virus</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fusarium graminearum</t>
+          <t>Wheat streak mosaic virus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fungal</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stem</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>Foliar, Whole plant</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Leaves show a yellowed mosaic pattern of parallel discontinuous streaks that progress to mottled yellow; plants become stunted, discolored, and rosetted.. Streaked mosaic pattern on leaves and rosette appearance of plants; mite-infested leaves have edges rolled inward toward the mid-rib, and new leaf tips trapped in rolled leaves form loops.</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>low</t>
@@ -1013,23 +1109,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pythium_Diseases</t>
+          <t>Rhizoctonia_Damping-Off</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pythium spp. (syn. Globisporangium spp.)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Rhizoctonia solani</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Root, Seed</t>
+          <t>Root</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Adult plants may be stunted and/or chlorotic, as if nitrogen deficient. Root length may be reduced. Heads may contain shriveled grain. Severe infections cause a general root rot.</t>
+          <t>Field symptoms include bare patches or areas of uneven plant height. Severe infection causes plants to be stunted, appear drought stressed or nutrient deprived, and may result in premature plant death.. Roots develop characteristically fine, sharp-looking, red-brown points known as spear tip. Girdling can also make roots look pinched or constricted.. Drought stress, Nutrient deficiency</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1044,12 +1144,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wheat_Stem_Rust</t>
+          <t>Septoria_Leaf_Blotch</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Puccinia graminis f. sp. tritici</t>
+          <t>Zymoseptoria tritici</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1059,12 +1159,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Foliar, Stem</t>
+          <t>Foliar, Seed</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Masses of red-brick urediniospores appearing on leaf sheaths, stems, glumes and awns of susceptible plants.. Distinctive red-brick colored urediniospores on stems and leaf sheaths, glumes and awns.</t>
+          <t>Elliptical, tan-brown lesions that often have yellowish halos first appear on seedling leaves. Lesion centers die and dark fruiting bodies are produced, giving the lesion a characteristic speckled appearance. Subsequent lesions on higher leaves generally follow leaf veins, having straight edges and no yellow margins.. Lesions generally do not have pronounced chlorotic halos like Stagonospora leaf and glume blotch and tan spot; lesions are more elongated with rougher edges. When humid, a translucent, curling thread of whitish ooze may appear from fruiting bodies.. Stagonospora leaf and glume blotch, Tan spot</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1079,12 +1179,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Septoria_Leaf_Blotch</t>
+          <t>Wheat_Leaf_Rust</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zymoseptoria tritici</t>
+          <t>Puccinia triticina</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1099,16 +1199,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Initially asymptomatic infection lasting 7-11 days post-infection, followed by necrotic symptoms as host cells lyse.. Prolonged latent asymptomatic phase of 7-11 days distinguishes it from other blotch pathogens.. Septoria nodorum blotch, Tan spot</t>
+          <t>Brown, generally circular uredinia appearing on the upper leaf surface that seldom penetrate through the leaf; with severe epidemics sheath infections can occur.. Brown, circular uredinia on upper leaf surface that seldom penetrate through the leaf; pustules are orange to brown, medium-size and round to slightly elongated, scattered randomly on leaf surface (not in stripes), developing at warmer temperatures (64-77°F).. Stripe Rust, Stem Rust</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1127,248 +1227,41 @@
           <t>Fungal</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Foliar, Stem, Seed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Small tan to brown lens or diamond-shaped spots on leaves that are elliptical to elongate with a dark brown center and yellow border; lesions coalesce into larger irregular dead tissue areas. Kernels may develop a red, dirty appearance known as red smudge.. Elliptical to elongate tan-colored spots with a dark brown spot near the center surrounded by a yellow border; a pinhead-size black spot may be present at the infection site; pseudothecia on stubble feel like coarse sandpaper. The yellow halo distinguishes it from Septoria tritici blotch, and lesions are more angular than Stagonospora leaf blotch.. Septoria tritici blotch, Stagonospora leaf blotch</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stem_Rust</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Puccinia graminis f. sp. tritici</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Stem, Foliar, Seed, Vascular</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Stem rust forms orange to dark red, elliptical to elongate pustules on stems, leaves, and leaf sheaths that cause conspicuous tears in epidermal tissues with tattered margins. Brick-red uredinia rupture the host epidermis on both leaf surfaces, and infected areas are rough to the touch. Severe infections weaken stems, leading to lodging and shriveled grain.. Pustules are larger than leaf rust and stripe rust, cause conspicuous epidermal tearing with tattered appearance, and are brick-red in color. They rupture host epidermis and sporulate on both leaf surfaces; infected areas are rough to the touch.. Leaf rust, Stripe rust, Oat crown rust, Barley crown rust</t>
-        </is>
-      </c>
+          <t>Take-All_Root_Rot</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Stripe_Rust</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Puccinia striiformis Westend. f. sp. tritici</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Foliar, Stem</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Linear arrangement of pustules on leaves producing yellow-orange pustules in susceptible cultivars, progressing to black-colored teliospores as the season advances.. Linear arrangement of pustules on leaves after middle jointing stage is the key distinguishing feature; yellow-orange colored pustules arranged in stripes in susceptible cultivars versus small flecks and chlorosis in resistant cultivars.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Take-All_Root_Rot</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Root, Stem</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Blackened roots and lower stems with seedling death and extensive plant stand failure</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Bacterial_Streak</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Resistance_Phenotype__Moderately_Resistant</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Resistance_Phenotype__Moderately_Susceptible</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Resistance_Phenotype__Resistant</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Resistance_Phenotype__Susceptible</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Wheat_Barley_Yellow_Dwarf</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Wheat_Cephalosporium_Stripe</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
         <v>0</v>
       </c>
     </row>
